--- a/design/捡漏_数值框架.xlsx
+++ b/design/捡漏_数值框架.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1359,6 +1359,73 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>结算与货币精度（T6 垃圾场结算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>结算单唯一出处</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>core/economy.settleBag —— 界面的每一个金额都取自它，不许自己再算一遍（T6 验收口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>取整规则</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>全程不取整：货币内部是精确浮点，显示统一保留两位小数（ui/format.ts）。逐件取整会把白档 0.68 元抹成 0；整趟取整会让「捡 6 个塑料瓶」变成 0 元 —— 两种都会废掉白档</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>入账时点</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>回程即入账，称重动画只回放已入账的数字（先入账再播动画，中途关页也不会白跑一趟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>经验</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>经验 = 合计金额 × level.expPerCurrency；等级与区域解锁随之刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>跑商空间</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>同一袋垃圾在不同区域的结算价不同（global.sell.zonePriceModifier 0.85–1.25），结算单里逐件展示三个系数</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
